--- a/samples/P_固定资产明细表.xlsx
+++ b/samples/P_固定资产明细表.xlsx
@@ -66,12 +66,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,170 +438,685 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>资产编号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>资产名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>资产类别</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>使用部门</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>购置日期</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>原值</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>累计折旧</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>净值</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>本年折旧</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>残值率</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>使用年限</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>本月折旧</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>GD-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>厂房A栋</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>房屋建筑物</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>生产部</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n">
         <v>8000000</v>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>6200000</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>200000</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="n">
+        <v>1520000</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>6480000</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>20年</t>
-        </is>
-      </c>
+      <c r="J2" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>31667</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>在用</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>机器设备</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>140000</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
+          <t>GD-002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>厂房B栋</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>房屋建筑物</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>生产部</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2020-03-01</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>760000</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>3240000</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>10年</t>
-        </is>
-      </c>
+      <c r="J3" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>15833</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>在用</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>运输设备</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>800000</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>250000</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>550000</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>40000</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+          <t>GD-003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>数控加工中心</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>机器设备</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>生产部</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2021-08-01</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>380000</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>820000</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5年</t>
-        </is>
-      </c>
+      <c r="J4" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>9500</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>在用</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>GD-004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>注塑机</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>机器设备</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>生产部</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>800000</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>228000</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>572000</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>6333</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>在用</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>GD-005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>工业机器人</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>机器设备</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>生产部</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>2800000</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>93333</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>2706667</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>22167</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>在用</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>本年新增，关注折旧起始月</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>GD-006</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>激光切割机</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>机器设备</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>生产部</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>295000</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>2375</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>在用</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>本年新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>GD-007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>商务车</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>运输工具</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>行政部</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>600000</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>171000</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>429000</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>5938</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>在用</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>GD-008</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>货车</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>运输工具</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>物流部</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>95000</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>405000</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>4948</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>在用</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>GD-009</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>叉车</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>运输工具</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>物流部</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>23750</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>476250</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>4948</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>在用</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>本年新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>GD-010</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>服务器集群</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>电子设备</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>370000</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>150000</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>220000</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>IT部</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>71250</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>228750</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3年</t>
-        </is>
-      </c>
+      <c r="J11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>4750</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>在用</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>GD-011</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>办公电脑</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>电子设备</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>行政部</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>200000</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>38000</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>162000</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>3167</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>在用</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
